--- a/output/details/2026-05-23/preprocessed_data.xlsx
+++ b/output/details/2026-05-23/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46165</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1133411025324073</v>
+        <v>-0.1172766437020819</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1562638833673312</v>
+        <v>-0.1393889555071768</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1560484830609669</v>
+        <v>-0.1391152302106672</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.121549192485307</v>
+        <v>0.003109251981494599</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00169945832446355</v>
+        <v>0.001696402037454521</v>
       </c>
       <c r="G2" t="n">
-        <v>1.919044072090043</v>
+        <v>2.484076982632957</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4432316345324194</v>
+        <v>-0.2687668485872157</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
